--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BDA50C-8B98-4BB1-84D6-1DCE97908476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BE902A-1E3C-4BDF-B888-EE95F23C7A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
@@ -2924,13 +2924,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:Q430" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:Q430" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="1962"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Q430" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
   <tableColumns count="17">
     <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2" dataDxfId="34"/>
     <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="33"/>
@@ -3407,7 +3401,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3438,10 +3432,13 @@
         <f>Tabela14[[#This Row],[PRECO 3%]]+(Tabela14[[#This Row],[PRECO 3%]]*0.06)</f>
         <v>0.43502399999999997</v>
       </c>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34">
-        <f>(Tabela14[[#This Row],[REGIÃO01-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO01-3%]]</f>
-        <v>0</v>
+      <c r="J2" s="49">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.1)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>0.45144000000000001</v>
+      </c>
+      <c r="K2" s="49">
+        <f>(Tabela14[[#This Row],[REGIÃO01-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO01-3%]]</f>
+        <v>0.47852640000000002</v>
       </c>
       <c r="L2" s="34">
         <f>(Tabela14[[#This Row],[PRECO 3%]]*0.05)+Tabela14[[#This Row],[PRECO 3%]]</f>
@@ -3468,7 +3465,7 @@
         <v>0.46112543999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3499,10 +3496,13 @@
         <f>Tabela14[[#This Row],[PRECO 3%]]+(Tabela14[[#This Row],[PRECO 3%]]*0.06)</f>
         <v>0.45792000000000005</v>
       </c>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34">
-        <f>(Tabela14[[#This Row],[REGIÃO01-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO01-3%]]</f>
-        <v>0</v>
+      <c r="J3" s="49">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.1)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>0.47520000000000007</v>
+      </c>
+      <c r="K3" s="49">
+        <f>(Tabela14[[#This Row],[REGIÃO01-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO01-3%]]</f>
+        <v>0.50371200000000005</v>
       </c>
       <c r="L3" s="34">
         <f>(Tabela14[[#This Row],[PRECO 3%]]*0.05)+Tabela14[[#This Row],[PRECO 3%]]</f>
@@ -3529,7 +3529,7 @@
         <v>0.48539520000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3560,10 +3560,13 @@
         <f>Tabela14[[#This Row],[PRECO 3%]]+(Tabela14[[#This Row],[PRECO 3%]]*0.06)</f>
         <v>0.48081600000000002</v>
       </c>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34">
-        <f>(Tabela14[[#This Row],[REGIÃO01-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO01-3%]]</f>
-        <v>0</v>
+      <c r="J4" s="49">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.1)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>0.49896000000000001</v>
+      </c>
+      <c r="K4" s="49">
+        <f>(Tabela14[[#This Row],[REGIÃO01-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO01-3%]]</f>
+        <v>0.52889759999999997</v>
       </c>
       <c r="L4" s="34">
         <f>(Tabela14[[#This Row],[PRECO 3%]]*0.05)+Tabela14[[#This Row],[PRECO 3%]]</f>
@@ -3590,7 +3593,7 @@
         <v>0.50966496000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3620,10 +3623,13 @@
         <f>Tabela14[[#This Row],[PRECO 3%]]+(Tabela14[[#This Row],[PRECO 3%]]*0.06)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34">
-        <f>(Tabela14[[#This Row],[REGIÃO01-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO01-3%]]</f>
-        <v>0</v>
+      <c r="J5" s="49" t="e">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.1)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K5" s="49" t="e">
+        <f>(Tabela14[[#This Row],[REGIÃO01-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO01-3%]]</f>
+        <v>#VALUE!</v>
       </c>
       <c r="L5" s="34" t="e">
         <f>(Tabela14[[#This Row],[PRECO 3%]]*0.05)+Tabela14[[#This Row],[PRECO 3%]]</f>
@@ -3650,7 +3656,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3714,7 +3720,7 @@
         <v>5.2359760000000009</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3778,7 +3784,7 @@
         <v>5.9839725714285725</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3842,7 +3848,7 @@
         <v>6.7319691428571433</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3905,7 +3911,7 @@
         <v>7.8539639999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3968,7 +3974,7 @@
         <v>8.2279622857142858</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4031,7 +4037,7 @@
         <v>8.9759588571428583</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4094,7 +4100,7 @@
         <v>9.7239554285714291</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4157,7 +4163,7 @@
         <v>10.471952000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4220,7 +4226,7 @@
         <v>12.224768000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4283,7 +4289,7 @@
         <v>11.967945142857145</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4346,7 +4352,7 @@
         <v>12.715941714285712</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4409,7 +4415,7 @@
         <v>13.463938285714287</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4472,7 +4478,7 @@
         <v>14.211934857142857</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4535,7 +4541,7 @@
         <v>14.95993142857143</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4598,7 +4604,7 @@
         <v>24.757723428571435</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>51</v>
       </c>
@@ -4661,7 +4667,7 @@
         <v>16.247256</v>
       </c>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>52</v>
       </c>
@@ -4724,7 +4730,7 @@
         <v>17.020934857142858</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>53</v>
       </c>
@@ -4787,7 +4793,7 @@
         <v>17.794613714285717</v>
       </c>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>54</v>
       </c>
@@ -4850,7 +4856,7 @@
         <v>18.568292571428572</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>55</v>
       </c>
@@ -4913,7 +4919,7 @@
         <v>19.34197142857143</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>56</v>
       </c>
@@ -4976,7 +4982,7 @@
         <v>20.115650285714288</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>57</v>
       </c>
@@ -5039,7 +5045,7 @@
         <v>20.889329142857143</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>58</v>
       </c>
@@ -5102,7 +5108,7 @@
         <v>21.663008000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>59</v>
       </c>
@@ -5165,7 +5171,7 @@
         <v>22.43668685714286</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>60</v>
       </c>
@@ -5228,7 +5234,7 @@
         <v>23.210365714285714</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>61</v>
       </c>
@@ -5291,7 +5297,7 @@
         <v>23.984044571428573</v>
       </c>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>63</v>
       </c>
@@ -5354,7 +5360,7 @@
         <v>19.40550833333333</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>73</v>
       </c>
@@ -5417,7 +5423,7 @@
         <v>34.573172</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>74</v>
       </c>
@@ -5480,7 +5486,7 @@
         <v>35.853659851851852</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>75</v>
       </c>
@@ -5543,7 +5549,7 @@
         <v>37.134147703703704</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>76</v>
       </c>
@@ -5605,7 +5611,7 @@
         <v>38.414635555555556</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>77</v>
       </c>
@@ -5668,7 +5674,7 @@
         <v>39.695123407407408</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>78</v>
       </c>
@@ -5731,7 +5737,7 @@
         <v>40.97561125925926</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>79</v>
       </c>
@@ -5794,7 +5800,7 @@
         <v>42.256099111111112</v>
       </c>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>80</v>
       </c>
@@ -5857,7 +5863,7 @@
         <v>43.536586962962964</v>
       </c>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>81</v>
       </c>
@@ -5920,7 +5926,7 @@
         <v>14.043929904761903</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>82</v>
       </c>
@@ -5983,7 +5989,7 @@
         <v>14.870043428571428</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>83</v>
       </c>
@@ -6046,7 +6052,7 @@
         <v>15.696156952380951</v>
       </c>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>84</v>
       </c>
@@ -6109,7 +6115,7 @@
         <v>16.522270476190474</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>85</v>
       </c>
@@ -6172,7 +6178,7 @@
         <v>17.348384000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>86</v>
       </c>
@@ -6235,7 +6241,7 @@
         <v>18.174497523809521</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>87</v>
       </c>
@@ -6298,7 +6304,7 @@
         <v>19.000611047619046</v>
       </c>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>88</v>
       </c>
@@ -6361,7 +6367,7 @@
         <v>19.826724571428571</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>89</v>
       </c>
@@ -6424,7 +6430,7 @@
         <v>20.652838095238096</v>
       </c>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>90</v>
       </c>
@@ -6487,7 +6493,7 @@
         <v>21.478951619047621</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>91</v>
       </c>
@@ -6550,7 +6556,7 @@
         <v>22.305065142857138</v>
       </c>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>92</v>
       </c>
@@ -6613,7 +6619,7 @@
         <v>23.131178666666663</v>
       </c>
     </row>
-    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>93</v>
       </c>
@@ -6676,7 +6682,7 @@
         <v>23.957292190476185</v>
       </c>
     </row>
-    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>94</v>
       </c>
@@ -6739,7 +6745,7 @@
         <v>24.783405714285713</v>
       </c>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>95</v>
       </c>
@@ -6802,7 +6808,7 @@
         <v>25.609519238095238</v>
       </c>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>96</v>
       </c>
@@ -6865,7 +6871,7 @@
         <v>26.43563276190476</v>
       </c>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>97</v>
       </c>
@@ -6928,7 +6934,7 @@
         <v>27.261746285714285</v>
       </c>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>129</v>
       </c>
@@ -6991,7 +6997,7 @@
         <v>30.634194810810815</v>
       </c>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>130</v>
       </c>
@@ -7054,7 +7060,7 @@
         <v>31.53520054054054</v>
       </c>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>131</v>
       </c>
@@ -7117,7 +7123,7 @@
         <v>32.436206270270276</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>132</v>
       </c>
@@ -7180,7 +7186,7 @@
         <v>33.337212000000008</v>
       </c>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>133</v>
       </c>
@@ -7243,7 +7249,7 @@
         <v>34.238217729729733</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>134</v>
       </c>
@@ -7306,7 +7312,7 @@
         <v>35.139223459459458</v>
       </c>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>135</v>
       </c>
@@ -7369,7 +7375,7 @@
         <v>36.040229189189191</v>
       </c>
     </row>
-    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>136</v>
       </c>
@@ -7432,7 +7438,7 @@
         <v>36.941234918918916</v>
       </c>
     </row>
-    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>152</v>
       </c>
@@ -7493,7 +7499,7 @@
         <v>0.53393472000000008</v>
       </c>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>153</v>
       </c>
@@ -7554,7 +7560,7 @@
         <v>0.57033935999999996</v>
       </c>
     </row>
-    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>154</v>
       </c>
@@ -7615,7 +7621,7 @@
         <v>0.59460911999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>155</v>
       </c>
@@ -7675,7 +7681,7 @@
         <v>79.775600000000011</v>
       </c>
     </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>157</v>
       </c>
@@ -7736,7 +7742,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>158</v>
       </c>
@@ -7797,7 +7803,7 @@
         <v>8.07800984</v>
       </c>
     </row>
-    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>159</v>
       </c>
@@ -7857,7 +7863,7 @@
         <v>5.2135040000000004</v>
       </c>
     </row>
-    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>160</v>
       </c>
@@ -7917,7 +7923,7 @@
         <v>7.3820519999999998</v>
       </c>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>161</v>
       </c>
@@ -7977,7 +7983,7 @@
         <v>9.4944199999999981</v>
       </c>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>162</v>
       </c>
@@ -8037,7 +8043,7 @@
         <v>14.134888</v>
       </c>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>163</v>
       </c>
@@ -8097,7 +8103,7 @@
         <v>4.4606920000000008</v>
       </c>
     </row>
-    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>164</v>
       </c>
@@ -8157,7 +8163,7 @@
         <v>6.3258679999999998</v>
       </c>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>165</v>
       </c>
@@ -8217,7 +8223,7 @@
         <v>8.1460999999999988</v>
       </c>
     </row>
-    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>166</v>
       </c>
@@ -8277,7 +8283,7 @@
         <v>12.067463999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>167</v>
       </c>
@@ -8337,7 +8343,7 @@
         <v>7.2022760000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>168</v>
       </c>
@@ -8397,7 +8403,7 @@
         <v>10.528131999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>169</v>
       </c>
@@ -8457,7 +8463,7 @@
         <v>13.516907999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>170</v>
       </c>
@@ -8517,7 +8523,7 @@
         <v>19.483224</v>
       </c>
     </row>
-    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>171</v>
       </c>
@@ -8577,7 +8583,7 @@
         <v>6.0449679999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>172</v>
       </c>
@@ -8637,7 +8643,7 @@
         <v>8.9213840000000015</v>
       </c>
     </row>
-    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>173</v>
       </c>
@@ -8697,7 +8703,7 @@
         <v>11.573080000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>174</v>
       </c>
@@ -8757,7 +8763,7 @@
         <v>16.561864</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>261</v>
       </c>
@@ -8820,7 +8826,7 @@
         <v>19.495808320000002</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>262</v>
       </c>
@@ -8883,7 +8889,7 @@
         <v>20.343452159999998</v>
       </c>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>263</v>
       </c>
@@ -8946,7 +8952,7 @@
         <v>21.191095999999998</v>
       </c>
     </row>
-    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>264</v>
       </c>
@@ -9009,7 +9015,7 @@
         <v>22.038739839999995</v>
       </c>
     </row>
-    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>265</v>
       </c>
@@ -9072,7 +9078,7 @@
         <v>22.886383680000002</v>
       </c>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>266</v>
       </c>
@@ -9135,7 +9141,7 @@
         <v>23.734027520000001</v>
       </c>
     </row>
-    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>267</v>
       </c>
@@ -9198,7 +9204,7 @@
         <v>24.581671359999998</v>
       </c>
     </row>
-    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>268</v>
       </c>
@@ -9261,7 +9267,7 @@
         <v>25.429315200000001</v>
       </c>
     </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>269</v>
       </c>
@@ -9324,7 +9330,7 @@
         <v>26.276959039999998</v>
       </c>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>270</v>
       </c>
@@ -9387,7 +9393,7 @@
         <v>26.700780960000003</v>
       </c>
     </row>
-    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>271</v>
       </c>
@@ -9450,7 +9456,7 @@
         <v>27.124602879999998</v>
       </c>
     </row>
-    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>272</v>
       </c>
@@ -9513,7 +9519,7 @@
         <v>27.972246719999998</v>
       </c>
     </row>
-    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>273</v>
       </c>
@@ -9576,7 +9582,7 @@
         <v>18.640523999999999</v>
       </c>
     </row>
-    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>274</v>
       </c>
@@ -9639,7 +9645,7 @@
         <v>19.528167999999997</v>
       </c>
     </row>
-    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>275</v>
       </c>
@@ -9702,7 +9708,7 @@
         <v>20.415812000000003</v>
       </c>
     </row>
-    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>276</v>
       </c>
@@ -9765,7 +9771,7 @@
         <v>21.303455999999997</v>
       </c>
     </row>
-    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>277</v>
       </c>
@@ -9828,7 +9834,7 @@
         <v>22.191099999999999</v>
       </c>
     </row>
-    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>278</v>
       </c>
@@ -9891,7 +9897,7 @@
         <v>23.078743999999997</v>
       </c>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>279</v>
       </c>
@@ -9954,7 +9960,7 @@
         <v>22.337167999999998</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>280</v>
       </c>
@@ -10017,7 +10023,7 @@
         <v>24.854032000000004</v>
       </c>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>281</v>
       </c>
@@ -10080,7 +10086,7 @@
         <v>25.741676000000002</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>282</v>
       </c>
@@ -10142,7 +10148,7 @@
         <v>26.62932</v>
       </c>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>283</v>
       </c>
@@ -10205,7 +10211,7 @@
         <v>27.516964000000002</v>
       </c>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>284</v>
       </c>
@@ -10268,7 +10274,7 @@
         <v>28.404608</v>
       </c>
     </row>
-    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>285</v>
       </c>
@@ -10331,7 +10337,7 @@
         <v>29.292251999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>286</v>
       </c>
@@ -10394,7 +10400,7 @@
         <v>30.179895999999999</v>
       </c>
     </row>
-    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>287</v>
       </c>
@@ -10457,7 +10463,7 @@
         <v>31.067539999999997</v>
       </c>
     </row>
-    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>288</v>
       </c>
@@ -10520,7 +10526,7 @@
         <v>31.955183999999999</v>
       </c>
     </row>
-    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>289</v>
       </c>
@@ -10583,7 +10589,7 @@
         <v>32.842827999999997</v>
       </c>
     </row>
-    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>290</v>
       </c>
@@ -10645,7 +10651,7 @@
         <v>30.742878736842101</v>
       </c>
     </row>
-    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>291</v>
       </c>
@@ -10708,7 +10714,7 @@
         <v>31.647081052631577</v>
       </c>
     </row>
-    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>292</v>
       </c>
@@ -10771,7 +10777,7 @@
         <v>32.551283368421046</v>
       </c>
     </row>
-    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>293</v>
       </c>
@@ -10834,7 +10840,7 @@
         <v>33.455485684210522</v>
       </c>
     </row>
-    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>294</v>
       </c>
@@ -10897,7 +10903,7 @@
         <v>34.359687999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>295</v>
       </c>
@@ -10960,7 +10966,7 @@
         <v>35.263890315789467</v>
       </c>
     </row>
-    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>296</v>
       </c>
@@ -11023,7 +11029,7 @@
         <v>36.168092631578943</v>
       </c>
     </row>
-    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>297</v>
       </c>
@@ -11086,7 +11092,7 @@
         <v>34.303233951219511</v>
       </c>
     </row>
-    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>298</v>
       </c>
@@ -11149,7 +11155,7 @@
         <v>35.20595063414634</v>
       </c>
     </row>
-    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>299</v>
       </c>
@@ -11212,7 +11218,7 @@
         <v>36.10866731707317</v>
       </c>
     </row>
-    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>300</v>
       </c>
@@ -11275,7 +11281,7 @@
         <v>37.011383999999993</v>
       </c>
     </row>
-    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>301</v>
       </c>
@@ -11338,7 +11344,7 @@
         <v>37.914100682926829</v>
       </c>
     </row>
-    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>302</v>
       </c>
@@ -11401,7 +11407,7 @@
         <v>38.816817365853659</v>
       </c>
     </row>
-    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>303</v>
       </c>
@@ -11464,7 +11470,7 @@
         <v>39.719534048780481</v>
       </c>
     </row>
-    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>304</v>
       </c>
@@ -11527,7 +11533,7 @@
         <v>40.622250731707311</v>
       </c>
     </row>
-    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>307</v>
       </c>
@@ -11590,7 +11596,7 @@
         <v>8.4183569230769226</v>
       </c>
     </row>
-    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>308</v>
       </c>
@@ -11653,7 +11659,7 @@
         <v>9.2601926153846179</v>
       </c>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>309</v>
       </c>
@@ -11716,7 +11722,7 @@
         <v>10.102028307692306</v>
       </c>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>310</v>
       </c>
@@ -11778,7 +11784,7 @@
         <v>10.943864000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>311</v>
       </c>
@@ -11841,7 +11847,7 @@
         <v>11.785699692307693</v>
       </c>
     </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>312</v>
       </c>
@@ -11904,7 +11910,7 @@
         <v>12.627535384615385</v>
       </c>
     </row>
-    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>313</v>
       </c>
@@ -11967,7 +11973,7 @@
         <v>13.460728</v>
       </c>
     </row>
-    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>314</v>
       </c>
@@ -12030,7 +12036,7 @@
         <v>14.31120676923077</v>
       </c>
     </row>
-    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>315</v>
       </c>
@@ -12093,7 +12099,7 @@
         <v>15.153042461538462</v>
       </c>
     </row>
-    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>316</v>
       </c>
@@ -12156,7 +12162,7 @@
         <v>15.994878153846155</v>
       </c>
     </row>
-    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>317</v>
       </c>
@@ -12219,7 +12225,7 @@
         <v>16.836713846153845</v>
       </c>
     </row>
-    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>318</v>
       </c>
@@ -12282,7 +12288,7 @@
         <v>17.678549538461539</v>
       </c>
     </row>
-    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>319</v>
       </c>
@@ -12345,7 +12351,7 @@
         <v>18.520385230769236</v>
       </c>
     </row>
-    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>320</v>
       </c>
@@ -12408,7 +12414,7 @@
         <v>19.362220923076926</v>
       </c>
     </row>
-    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>321</v>
       </c>
@@ -12471,7 +12477,7 @@
         <v>8.8764400000000006</v>
       </c>
     </row>
-    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>322</v>
       </c>
@@ -12534,7 +12540,7 @@
         <v>9.7640839999999987</v>
       </c>
     </row>
-    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>323</v>
       </c>
@@ -12597,7 +12603,7 @@
         <v>10.651728</v>
       </c>
     </row>
-    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>324</v>
       </c>
@@ -12660,7 +12666,7 @@
         <v>11.539371999999998</v>
       </c>
     </row>
-    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>325</v>
       </c>
@@ -12722,7 +12728,7 @@
         <v>12.427016000000002</v>
       </c>
     </row>
-    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>326</v>
       </c>
@@ -12785,7 +12791,7 @@
         <v>13.31466</v>
       </c>
     </row>
-    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>327</v>
       </c>
@@ -12848,7 +12854,7 @@
         <v>14.202304</v>
       </c>
     </row>
-    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>328</v>
       </c>
@@ -12911,7 +12917,7 @@
         <v>15.089948</v>
       </c>
     </row>
-    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>329</v>
       </c>
@@ -12974,7 +12980,7 @@
         <v>15.977592</v>
       </c>
     </row>
-    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>330</v>
       </c>
@@ -13037,7 +13043,7 @@
         <v>16.865235999999999</v>
       </c>
     </row>
-    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>331</v>
       </c>
@@ -13100,7 +13106,7 @@
         <v>17.752880000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>332</v>
       </c>
@@ -13163,7 +13169,7 @@
         <v>18.640523999999999</v>
       </c>
     </row>
-    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>333</v>
       </c>
@@ -13226,7 +13232,7 @@
         <v>19.528167999999997</v>
       </c>
     </row>
-    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>334</v>
       </c>
@@ -13289,7 +13295,7 @@
         <v>20.415812000000003</v>
       </c>
     </row>
-    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>335</v>
       </c>
@@ -13352,7 +13358,7 @@
         <v>21.303456000000001</v>
       </c>
     </row>
-    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>336</v>
       </c>
@@ -13415,7 +13421,7 @@
         <v>22.191099999999999</v>
       </c>
     </row>
-    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>337</v>
       </c>
@@ -13478,7 +13484,7 @@
         <v>23.078743999999997</v>
       </c>
     </row>
-    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>339</v>
       </c>
@@ -13540,7 +13546,7 @@
         <v>18.629287999999999</v>
       </c>
     </row>
-    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>340</v>
       </c>
@@ -13603,7 +13609,7 @@
         <v>20.181728666666661</v>
       </c>
     </row>
-    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>341</v>
       </c>
@@ -13666,7 +13672,7 @@
         <v>20.957948999999996</v>
       </c>
     </row>
-    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>342</v>
       </c>
@@ -13729,7 +13735,7 @@
         <v>21.734169333333327</v>
       </c>
     </row>
-    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>343</v>
       </c>
@@ -13792,7 +13798,7 @@
         <v>22.510389666666669</v>
       </c>
     </row>
-    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>344</v>
       </c>
@@ -13855,7 +13861,7 @@
         <v>23.28661</v>
       </c>
     </row>
-    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>345</v>
       </c>
@@ -13918,7 +13924,7 @@
         <v>24.062830333333331</v>
       </c>
     </row>
-    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>346</v>
       </c>
@@ -13981,7 +13987,7 @@
         <v>24.839050666666665</v>
       </c>
     </row>
-    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>347</v>
       </c>
@@ -14044,7 +14050,7 @@
         <v>25.615271</v>
       </c>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>348</v>
       </c>
@@ -14107,7 +14113,7 @@
         <v>26.391491333333331</v>
       </c>
     </row>
-    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>349</v>
       </c>
@@ -14170,7 +14176,7 @@
         <v>21.595591999999996</v>
       </c>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>350</v>
       </c>
@@ -14233,7 +14239,7 @@
         <v>22.395428740740741</v>
       </c>
     </row>
-    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>351</v>
       </c>
@@ -14296,7 +14302,7 @@
         <v>23.195265481481478</v>
       </c>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>352</v>
       </c>
@@ -14359,7 +14365,7 @@
         <v>23.995102222222219</v>
       </c>
     </row>
-    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>353</v>
       </c>
@@ -14422,7 +14428,7 @@
         <v>24.794938962962963</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>354</v>
       </c>
@@ -14485,7 +14491,7 @@
         <v>25.594775703703704</v>
       </c>
     </row>
-    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>355</v>
       </c>
@@ -14548,7 +14554,7 @@
         <v>26.394612444444444</v>
       </c>
     </row>
-    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>356</v>
       </c>
@@ -14611,7 +14617,7 @@
         <v>27.194449185185182</v>
       </c>
     </row>
-    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>357</v>
       </c>
@@ -14674,7 +14680,7 @@
         <v>17.800520639999998</v>
       </c>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>358</v>
       </c>
@@ -14737,7 +14743,7 @@
         <v>18.648164479999998</v>
       </c>
     </row>
-    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>359</v>
       </c>
@@ -14800,7 +14806,7 @@
         <v>17.752880000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>414</v>
       </c>
@@ -14860,7 +14866,7 @@
         <v>4.3258600000000005</v>
       </c>
     </row>
-    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>416</v>
       </c>
@@ -14920,7 +14926,7 @@
         <v>5.2135040000000004</v>
       </c>
     </row>
-    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>417</v>
       </c>
@@ -14980,7 +14986,7 @@
         <v>6.0449679999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>418</v>
       </c>
@@ -15040,7 +15046,7 @@
         <v>7.2022760000000003</v>
       </c>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>419</v>
       </c>
@@ -15100,7 +15106,7 @@
         <v>6.1460919999999994</v>
       </c>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>420</v>
       </c>
@@ -15160,7 +15166,7 @@
         <v>7.3820519999999998</v>
       </c>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>421</v>
       </c>
@@ -15220,7 +15226,7 @@
         <v>8.9213840000000015</v>
       </c>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>422</v>
       </c>
@@ -15280,7 +15286,7 @@
         <v>10.528131999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>423</v>
       </c>
@@ -15340,7 +15346,7 @@
         <v>7.8989080000000005</v>
       </c>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>424</v>
       </c>
@@ -15400,7 +15406,7 @@
         <v>9.4944199999999981</v>
       </c>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>425</v>
       </c>
@@ -15460,7 +15466,7 @@
         <v>11.573080000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>426</v>
       </c>
@@ -15520,7 +15526,7 @@
         <v>13.516907999999999</v>
       </c>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>427</v>
       </c>
@@ -15580,7 +15586,7 @@
         <v>12.067463999999999</v>
       </c>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>428</v>
       </c>
@@ -15640,7 +15646,7 @@
         <v>14.134888</v>
       </c>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>429</v>
       </c>
@@ -15700,7 +15706,7 @@
         <v>16.561864</v>
       </c>
     </row>
-    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>430</v>
       </c>
@@ -15760,7 +15766,7 @@
         <v>19.483224</v>
       </c>
     </row>
-    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>474</v>
       </c>
@@ -15820,7 +15826,7 @@
         <v>7.6180079999999997</v>
       </c>
     </row>
-    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>475</v>
       </c>
@@ -15880,7 +15886,7 @@
         <v>8.8989119999999993</v>
       </c>
     </row>
-    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>476</v>
       </c>
@@ -15940,7 +15946,7 @@
         <v>5.5168759999999999</v>
       </c>
     </row>
-    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>477</v>
       </c>
@@ -16000,7 +16006,7 @@
         <v>6.4494640000000008</v>
       </c>
     </row>
-    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>478</v>
       </c>
@@ -16060,7 +16066,7 @@
         <v>7.6180079999999997</v>
       </c>
     </row>
-    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>479</v>
       </c>
@@ -16120,7 +16126,7 @@
         <v>8.8989119999999993</v>
       </c>
     </row>
-    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>480</v>
       </c>
@@ -16180,7 +16186,7 @@
         <v>5.5168759999999999</v>
       </c>
     </row>
-    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>481</v>
       </c>
@@ -16240,7 +16246,7 @@
         <v>6.4494640000000008</v>
       </c>
     </row>
-    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>495</v>
       </c>
@@ -16297,7 +16303,7 @@
         <v>44.943999999999996</v>
       </c>
     </row>
-    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>730</v>
       </c>
@@ -16357,7 +16363,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>731</v>
       </c>
@@ -16417,7 +16423,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>1209</v>
       </c>
@@ -16477,7 +16483,7 @@
         <v>97.191400000000002</v>
       </c>
     </row>
-    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>1586</v>
       </c>
@@ -16537,7 +16543,7 @@
         <v>55.618200000000002</v>
       </c>
     </row>
-    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>1587</v>
       </c>
@@ -16598,7 +16604,7 @@
         <v>3.2404623999999997</v>
       </c>
     </row>
-    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>1588</v>
       </c>
@@ -16659,7 +16665,7 @@
         <v>5.9948554399999994</v>
       </c>
     </row>
-    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>1589</v>
       </c>
@@ -16719,7 +16725,7 @@
         <v>4.8202439999999998</v>
       </c>
     </row>
-    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>1589</v>
       </c>
@@ -16775,7 +16781,7 @@
         <v>4.8175473599999998</v>
       </c>
     </row>
-    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>1590</v>
       </c>
@@ -16835,7 +16841,7 @@
         <v>5.9550799999999997</v>
       </c>
     </row>
-    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>1590</v>
       </c>
@@ -16891,7 +16897,7 @@
         <v>5.9582260800000002</v>
       </c>
     </row>
-    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>1592</v>
       </c>
@@ -16951,7 +16957,7 @@
         <v>6.8314880000000002</v>
       </c>
     </row>
-    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>1592</v>
       </c>
@@ -17007,7 +17013,7 @@
         <v>6.8319374399999999</v>
       </c>
     </row>
-    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>1593</v>
       </c>
@@ -17067,7 +17073,7 @@
         <v>8.7977879999999988</v>
       </c>
     </row>
-    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>1593</v>
       </c>
@@ -17123,7 +17129,7 @@
         <v>8.7977879999999988</v>
       </c>
     </row>
-    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>1594</v>
       </c>
@@ -17183,7 +17189,7 @@
         <v>13.033759999999999</v>
       </c>
     </row>
-    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>1594</v>
       </c>
@@ -17239,7 +17245,7 @@
         <v>13.03286112</v>
       </c>
     </row>
-    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>1595</v>
       </c>
@@ -17299,7 +17305,7 @@
         <v>6.5281159999999998</v>
       </c>
     </row>
-    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>1595</v>
       </c>
@@ -17355,7 +17361,7 @@
         <v>6.5285654399999995</v>
       </c>
     </row>
-    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>1596</v>
       </c>
@@ -17415,7 +17421,7 @@
         <v>8.2247520000000005</v>
       </c>
     </row>
-    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>1596</v>
       </c>
@@ -17471,7 +17477,7 @@
         <v>8.2274486400000004</v>
       </c>
     </row>
-    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>1597</v>
       </c>
@@ -17531,7 +17537,7 @@
         <v>9.6404879999999995</v>
       </c>
     </row>
-    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>1597</v>
       </c>
@@ -17587,7 +17593,7 @@
         <v>9.6350947199999997</v>
       </c>
     </row>
-    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>1598</v>
       </c>
@@ -17647,7 +17653,7 @@
         <v>12.494431999999998</v>
       </c>
     </row>
-    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>1598</v>
       </c>
@@ -17703,7 +17709,7 @@
         <v>12.498926400000002</v>
       </c>
     </row>
-    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>1599</v>
       </c>
@@ -17763,7 +17769,7 @@
         <v>17.887712000000001</v>
       </c>
     </row>
-    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>1599</v>
       </c>
@@ -17819,7 +17825,7 @@
         <v>17.886813120000003</v>
       </c>
     </row>
-    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>1600</v>
       </c>
@@ -17879,7 +17885,7 @@
         <v>5.2135040000000004</v>
       </c>
     </row>
-    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>1601</v>
       </c>
@@ -17939,7 +17945,7 @@
         <v>6.4494640000000008</v>
       </c>
     </row>
-    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>1602</v>
       </c>
@@ -17999,7 +18005,7 @@
         <v>7.3820519999999998</v>
       </c>
     </row>
-    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>1603</v>
       </c>
@@ -18059,7 +18065,7 @@
         <v>9.4944199999999981</v>
       </c>
     </row>
-    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>1604</v>
       </c>
@@ -18119,7 +18125,7 @@
         <v>14.134888</v>
       </c>
     </row>
-    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>1605</v>
       </c>
@@ -18179,7 +18185,7 @@
         <v>7.2022760000000003</v>
       </c>
     </row>
-    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>1606</v>
       </c>
@@ -18239,7 +18245,7 @@
         <v>8.8989119999999993</v>
       </c>
     </row>
-    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>1608</v>
       </c>
@@ -18299,7 +18305,7 @@
         <v>10.528131999999999</v>
       </c>
     </row>
-    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>1609</v>
       </c>
@@ -18359,7 +18365,7 @@
         <v>13.516907999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>1610</v>
       </c>
@@ -18419,7 +18425,7 @@
         <v>19.483224</v>
       </c>
     </row>
-    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>1611</v>
       </c>
@@ -18479,7 +18485,7 @@
         <v>5.8539560000000002</v>
       </c>
     </row>
-    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>1611</v>
       </c>
@@ -18535,7 +18541,7 @@
         <v>6.3222724800000005</v>
       </c>
     </row>
-    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>1612</v>
       </c>
@@ -18595,7 +18601,7 @@
         <v>7.3932880000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>1612</v>
       </c>
@@ -18651,7 +18657,7 @@
         <v>7.984751039999999</v>
       </c>
     </row>
-    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>1613</v>
       </c>
@@ -18711,7 +18717,7 @@
         <v>8.651720000000001</v>
       </c>
     </row>
-    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>1613</v>
       </c>
@@ -18767,7 +18773,7 @@
         <v>9.3438576000000015</v>
       </c>
     </row>
-    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>1614</v>
       </c>
@@ -18827,7 +18833,7 @@
         <v>11.224763999999999</v>
       </c>
     </row>
-    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>1614</v>
       </c>
@@ -18883,7 +18889,7 @@
         <v>12.122745120000001</v>
       </c>
     </row>
-    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>1615</v>
       </c>
@@ -18943,7 +18949,7 @@
         <v>16.06748</v>
       </c>
     </row>
-    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A254" s="19">
         <v>1615</v>
       </c>
@@ -19000,7 +19006,7 @@
         <v>17.352878400000002</v>
       </c>
     </row>
-    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>1616</v>
       </c>
@@ -19060,7 +19066,7 @@
         <v>4.3258600000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A256" s="6">
         <v>1616</v>
       </c>
@@ -19116,7 +19122,7 @@
         <v>4.6719288000000008</v>
       </c>
     </row>
-    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>1617</v>
       </c>
@@ -19176,7 +19182,7 @@
         <v>5.3483359999999998</v>
       </c>
     </row>
-    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A258" s="6">
         <v>1617</v>
       </c>
@@ -19232,7 +19238,7 @@
         <v>5.7762028799999996</v>
       </c>
     </row>
-    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>1618</v>
       </c>
@@ -19292,7 +19298,7 @@
         <v>6.1460919999999994</v>
       </c>
     </row>
-    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A260" s="6">
         <v>1618</v>
       </c>
@@ -19348,7 +19354,7 @@
         <v>6.6377793599999997</v>
       </c>
     </row>
-    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>1619</v>
       </c>
@@ -19408,7 +19414,7 @@
         <v>7.8989080000000005</v>
       </c>
     </row>
-    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A262" s="6">
         <v>1619</v>
       </c>
@@ -19464,7 +19470,7 @@
         <v>8.5308206400000017</v>
       </c>
     </row>
-    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>1620</v>
       </c>
@@ -19524,7 +19530,7 @@
         <v>11.707912</v>
       </c>
     </row>
-    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A264" s="6">
         <v>1620</v>
       </c>
@@ -19580,7 +19586,7 @@
         <v>12.644544960000001</v>
       </c>
     </row>
-    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>1621</v>
       </c>
@@ -19640,7 +19646,7 @@
         <v>5.2135040000000004</v>
       </c>
     </row>
-    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>1622</v>
       </c>
@@ -19700,7 +19706,7 @@
         <v>6.4494640000000008</v>
       </c>
     </row>
-    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>1623</v>
       </c>
@@ -19760,7 +19766,7 @@
         <v>7.3820519999999998</v>
       </c>
     </row>
-    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>1624</v>
       </c>
@@ -19820,7 +19826,7 @@
         <v>9.4944199999999981</v>
       </c>
     </row>
-    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>1625</v>
       </c>
@@ -19880,7 +19886,7 @@
         <v>14.134888</v>
       </c>
     </row>
-    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>1626</v>
       </c>
@@ -19940,7 +19946,7 @@
         <v>7.2022760000000003</v>
       </c>
     </row>
-    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>1627</v>
       </c>
@@ -20000,7 +20006,7 @@
         <v>8.8989119999999993</v>
       </c>
     </row>
-    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>1628</v>
       </c>
@@ -20060,7 +20066,7 @@
         <v>10.528131999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>1629</v>
       </c>
@@ -20120,7 +20126,7 @@
         <v>13.516907999999999</v>
       </c>
     </row>
-    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>1630</v>
       </c>
@@ -20180,7 +20186,7 @@
         <v>19.483224</v>
       </c>
     </row>
-    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>1636</v>
       </c>
@@ -20240,7 +20246,7 @@
         <v>18.054333658536585</v>
       </c>
     </row>
-    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>1637</v>
       </c>
@@ -20300,7 +20306,7 @@
         <v>20.76248370731707</v>
       </c>
     </row>
-    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>1639</v>
       </c>
@@ -20360,7 +20366,7 @@
         <v>4.9532782399999995</v>
       </c>
     </row>
-    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>1640</v>
       </c>
@@ -20420,7 +20426,7 @@
         <v>8.9438560000000003</v>
       </c>
     </row>
-    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>1641</v>
       </c>
@@ -20480,7 +20486,7 @@
         <v>0.7280928000000001</v>
       </c>
     </row>
-    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>1642</v>
       </c>
@@ -20540,7 +20546,7 @@
         <v>0.7523625599999999</v>
       </c>
     </row>
-    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>1643</v>
       </c>
@@ -20601,7 +20607,7 @@
         <v>0.78876720000000011</v>
       </c>
     </row>
-    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>1644</v>
       </c>
@@ -20661,7 +20667,7 @@
         <v>4.4382200000000003</v>
       </c>
     </row>
-    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A283" s="6">
         <v>1644</v>
       </c>
@@ -20717,7 +20723,7 @@
         <v>4.4413660800000008</v>
       </c>
     </row>
-    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>1646</v>
       </c>
@@ -20777,7 +20783,7 @@
         <v>4.4606920000000008</v>
       </c>
     </row>
-    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>1647</v>
       </c>
@@ -20837,7 +20843,7 @@
         <v>5.5168759999999999</v>
       </c>
     </row>
-    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>1648</v>
       </c>
@@ -20897,7 +20903,7 @@
         <v>6.3258679999999998</v>
       </c>
     </row>
-    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>1649</v>
       </c>
@@ -20957,7 +20963,7 @@
         <v>8.1460999999999988</v>
       </c>
     </row>
-    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>1650</v>
       </c>
@@ -21017,7 +21023,7 @@
         <v>12.067463999999999</v>
       </c>
     </row>
-    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>1651</v>
       </c>
@@ -21077,7 +21083,7 @@
         <v>6.0449679999999999</v>
       </c>
     </row>
-    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>1652</v>
       </c>
@@ -21137,7 +21143,7 @@
         <v>7.6180079999999997</v>
       </c>
     </row>
-    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>1653</v>
       </c>
@@ -21197,7 +21203,7 @@
         <v>8.9213840000000015</v>
       </c>
     </row>
-    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>1654</v>
       </c>
@@ -21257,7 +21263,7 @@
         <v>11.573080000000001</v>
       </c>
     </row>
-    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>1655</v>
       </c>
@@ -21317,7 +21323,7 @@
         <v>16.561864</v>
       </c>
     </row>
-    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>1656</v>
       </c>
@@ -21377,7 +21383,7 @@
         <v>5.6292359999999997</v>
       </c>
     </row>
-    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A295" s="6">
         <v>1656</v>
       </c>
@@ -21433,7 +21439,7 @@
         <v>5.6305843199999988</v>
       </c>
     </row>
-    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>1657</v>
       </c>
@@ -21493,7 +21499,7 @@
         <v>6.9663199999999996</v>
       </c>
     </row>
-    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A297" s="6">
         <v>1657</v>
       </c>
@@ -21549,7 +21555,7 @@
         <v>6.9654211200000002</v>
       </c>
     </row>
-    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>1658</v>
       </c>
@@ -21609,7 +21615,7 @@
         <v>7.9775599999999995</v>
       </c>
     </row>
-    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A299" s="6">
         <v>1658</v>
       </c>
@@ -21665,7 +21671,7 @@
         <v>7.9726161599999994</v>
       </c>
     </row>
-    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>1659</v>
       </c>
@@ -21725,7 +21731,7 @@
         <v>10.258468000000001</v>
       </c>
     </row>
-    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A301" s="6">
         <v>1659</v>
       </c>
@@ -21781,7 +21787,7 @@
         <v>10.2539736</v>
       </c>
     </row>
-    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>1660</v>
       </c>
@@ -21841,7 +21847,7 @@
         <v>15.269724</v>
       </c>
     </row>
-    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A303" s="6">
         <v>1660</v>
       </c>
@@ -21897,7 +21903,7 @@
         <v>15.26567904</v>
       </c>
     </row>
-    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>1661</v>
       </c>
@@ -21957,7 +21963,7 @@
         <v>7.2022760000000003</v>
       </c>
     </row>
-    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A305" s="6">
         <v>1661</v>
       </c>
@@ -22013,7 +22019,7 @@
         <v>7.7784580800000001</v>
       </c>
     </row>
-    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>1662</v>
       </c>
@@ -22073,7 +22079,7 @@
         <v>8.8989119999999993</v>
       </c>
     </row>
-    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A307" s="6">
         <v>1662</v>
       </c>
@@ -22129,7 +22135,7 @@
         <v>9.6108249599999986</v>
       </c>
     </row>
-    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>1663</v>
       </c>
@@ -22189,7 +22195,7 @@
         <v>10.528131999999999</v>
       </c>
     </row>
-    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A309" s="6">
         <v>1663</v>
       </c>
@@ -22245,7 +22251,7 @@
         <v>11.370382559999998</v>
       </c>
     </row>
-    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>1664</v>
       </c>
@@ -22305,7 +22311,7 @@
         <v>13.516907999999999</v>
       </c>
     </row>
-    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A311" s="6">
         <v>1664</v>
       </c>
@@ -22361,7 +22367,7 @@
         <v>14.598260639999999</v>
       </c>
     </row>
-    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>1665</v>
       </c>
@@ -22421,7 +22427,7 @@
         <v>19.483224</v>
       </c>
     </row>
-    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A313" s="6">
         <v>1665</v>
       </c>
@@ -22477,7 +22483,7 @@
         <v>21.041881920000002</v>
       </c>
     </row>
-    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>1666</v>
       </c>
@@ -22537,7 +22543,7 @@
         <v>4.4606920000000008</v>
       </c>
     </row>
-    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>1667</v>
       </c>
@@ -22597,7 +22603,7 @@
         <v>5.5168759999999999</v>
       </c>
     </row>
-    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>1668</v>
       </c>
@@ -22657,7 +22663,7 @@
         <v>6.3258679999999998</v>
       </c>
     </row>
-    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>1669</v>
       </c>
@@ -22717,7 +22723,7 @@
         <v>8.1460999999999988</v>
       </c>
     </row>
-    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>1670</v>
       </c>
@@ -22777,7 +22783,7 @@
         <v>12.067463999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>1671</v>
       </c>
@@ -22837,7 +22843,7 @@
         <v>6.0449679999999999</v>
       </c>
     </row>
-    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>1672</v>
       </c>
@@ -22897,7 +22903,7 @@
         <v>7.6180079999999997</v>
       </c>
     </row>
-    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>1673</v>
       </c>
@@ -22957,7 +22963,7 @@
         <v>8.9213840000000015</v>
       </c>
     </row>
-    <row r="322" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>1674</v>
       </c>
@@ -23017,7 +23023,7 @@
         <v>11.573080000000001</v>
       </c>
     </row>
-    <row r="323" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>1675</v>
       </c>
@@ -23077,7 +23083,7 @@
         <v>16.561864</v>
       </c>
     </row>
-    <row r="324" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>1676</v>
       </c>
@@ -23137,7 +23143,7 @@
         <v>5.2135040000000004</v>
       </c>
     </row>
-    <row r="325" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>1677</v>
       </c>
@@ -23197,7 +23203,7 @@
         <v>6.4494640000000008</v>
       </c>
     </row>
-    <row r="326" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>1678</v>
       </c>
@@ -23257,7 +23263,7 @@
         <v>7.3820519999999998</v>
       </c>
     </row>
-    <row r="327" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>1679</v>
       </c>
@@ -23317,7 +23323,7 @@
         <v>9.4944199999999981</v>
       </c>
     </row>
-    <row r="328" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>1680</v>
       </c>
@@ -23377,7 +23383,7 @@
         <v>14.134888</v>
       </c>
     </row>
-    <row r="329" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>1681</v>
       </c>
@@ -23437,7 +23443,7 @@
         <v>7.2022760000000003</v>
       </c>
     </row>
-    <row r="330" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>1682</v>
       </c>
@@ -23497,7 +23503,7 @@
         <v>8.8989119999999993</v>
       </c>
     </row>
-    <row r="331" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>1683</v>
       </c>
@@ -23557,7 +23563,7 @@
         <v>10.528131999999999</v>
       </c>
     </row>
-    <row r="332" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>1684</v>
       </c>
@@ -23617,7 +23623,7 @@
         <v>13.516907999999999</v>
       </c>
     </row>
-    <row r="333" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>1685</v>
       </c>
@@ -23677,7 +23683,7 @@
         <v>19.483224</v>
       </c>
     </row>
-    <row r="334" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>1687</v>
       </c>
@@ -23740,7 +23746,7 @@
         <v>21.700855578947365</v>
       </c>
     </row>
-    <row r="335" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>1690</v>
       </c>
@@ -23803,7 +23809,7 @@
         <v>21.045892307692306</v>
       </c>
     </row>
-    <row r="336" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>1697</v>
       </c>
@@ -23866,7 +23872,7 @@
         <v>33.672887500000002</v>
       </c>
     </row>
-    <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>1699</v>
       </c>
@@ -23929,7 +23935,7 @@
         <v>15.196898074074074</v>
       </c>
     </row>
-    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>1700</v>
       </c>
@@ -23992,7 +23998,7 @@
         <v>32.325972</v>
       </c>
     </row>
-    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>1754</v>
       </c>
@@ -24055,7 +24061,7 @@
         <v>31.325968000000003</v>
       </c>
     </row>
-    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>1773</v>
       </c>
@@ -24118,7 +24124,7 @@
         <v>16.796571555555555</v>
       </c>
     </row>
-    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>1774</v>
       </c>
@@ -24181,7 +24187,7 @@
         <v>32.817680761904761</v>
       </c>
     </row>
-    <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>1775</v>
       </c>
@@ -24244,7 +24250,7 @@
         <v>36.040229189189191</v>
       </c>
     </row>
-    <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>1776</v>
       </c>
@@ -24307,7 +24313,7 @@
         <v>36.941234918918916</v>
       </c>
     </row>
-    <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>1777</v>
       </c>
@@ -24370,7 +24376,7 @@
         <v>37.842240648648655</v>
       </c>
     </row>
-    <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>1778</v>
       </c>
@@ -24433,7 +24439,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>1779</v>
       </c>
@@ -24496,7 +24502,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="347" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>1780</v>
       </c>
@@ -24559,7 +24565,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>1781</v>
       </c>
@@ -24622,7 +24628,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>1782</v>
       </c>
@@ -24685,7 +24691,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="350" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>1787</v>
       </c>
@@ -24748,7 +24754,7 @@
         <v>5.1797960000000005</v>
       </c>
     </row>
-    <row r="351" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A351" s="6">
         <v>1787</v>
       </c>
@@ -24807,7 +24813,7 @@
         <v>5.1815937599999993</v>
       </c>
     </row>
-    <row r="352" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>1797</v>
       </c>
@@ -24864,7 +24870,7 @@
         <v>54.494599999999998</v>
       </c>
     </row>
-    <row r="353" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>1819</v>
       </c>
@@ -24927,7 +24933,7 @@
         <v>18.955132000000003</v>
       </c>
     </row>
-    <row r="354" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>1822</v>
       </c>
@@ -24990,7 +24996,7 @@
         <v>27.539436000000002</v>
       </c>
     </row>
-    <row r="355" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A355" s="6">
         <v>1960</v>
       </c>
@@ -25052,7 +25058,7 @@
         <v>106.607168</v>
       </c>
     </row>
-    <row r="356" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A356" s="6">
         <v>1961</v>
       </c>
@@ -25176,7 +25182,7 @@
         <v>120.719584</v>
       </c>
     </row>
-    <row r="358" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A358" s="6">
         <v>1963</v>
       </c>
@@ -25232,7 +25238,7 @@
         <v>5.4606960000000004</v>
       </c>
     </row>
-    <row r="359" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A359" s="6">
         <v>1964</v>
       </c>
@@ -25288,7 +25294,7 @@
         <v>6.7591281599999995</v>
       </c>
     </row>
-    <row r="360" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A360" s="6">
         <v>1965</v>
       </c>
@@ -25344,7 +25350,7 @@
         <v>7.7420534399999994</v>
       </c>
     </row>
-    <row r="361" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A361" s="6">
         <v>1966</v>
       </c>
@@ -25400,7 +25406,7 @@
         <v>9.9384667199999992</v>
       </c>
     </row>
-    <row r="362" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A362" s="6">
         <v>1967</v>
       </c>
@@ -25456,7 +25462,7 @@
         <v>14.816688480000002</v>
       </c>
     </row>
-    <row r="363" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A363" s="6">
         <v>1968</v>
       </c>
@@ -25512,7 +25518,7 @@
         <v>7.5600302400000006</v>
       </c>
     </row>
-    <row r="364" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A364" s="6">
         <v>1969</v>
       </c>
@@ -25568,7 +25574,7 @@
         <v>9.3074529600000009</v>
       </c>
     </row>
-    <row r="365" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A365" s="6">
         <v>1970</v>
       </c>
@@ -25624,7 +25630,7 @@
         <v>11.01847104</v>
       </c>
     </row>
-    <row r="366" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A366" s="6">
         <v>1971</v>
       </c>
@@ -25680,7 +25686,7 @@
         <v>14.16140496</v>
       </c>
     </row>
-    <row r="367" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A367" s="19">
         <v>1972</v>
       </c>
@@ -25737,7 +25743,7 @@
         <v>20.423003039999998</v>
       </c>
     </row>
-    <row r="368" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A368" s="6">
         <v>1973</v>
       </c>
@@ -25793,7 +25799,7 @@
         <v>6.0189004799999992</v>
       </c>
     </row>
-    <row r="369" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A369" s="6">
         <v>1974</v>
       </c>
@@ -25849,7 +25855,7 @@
         <v>7.1595792000000005</v>
       </c>
     </row>
-    <row r="370" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A370" s="6">
         <v>1974</v>
       </c>
@@ -25905,7 +25911,7 @@
         <v>7.1573320000000002</v>
       </c>
     </row>
-    <row r="371" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>2010</v>
       </c>
@@ -25968,7 +25974,7 @@
         <v>28.887756</v>
       </c>
     </row>
-    <row r="372" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>2011</v>
       </c>
@@ -26031,7 +26037,7 @@
         <v>65.842960000000005</v>
       </c>
     </row>
-    <row r="373" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>2019</v>
       </c>
@@ -26094,7 +26100,7 @@
         <v>25.606843999999999</v>
       </c>
     </row>
-    <row r="374" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B374" t="s">
         <v>27</v>
       </c>
@@ -26148,7 +26154,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="375" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B375" t="s">
         <v>27</v>
       </c>
@@ -26202,7 +26208,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="376" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B376" t="s">
         <v>27</v>
       </c>
@@ -26256,7 +26262,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="377" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B377" t="s">
         <v>27</v>
       </c>
@@ -26310,7 +26316,7 @@
         <v>4.7977719999999993</v>
       </c>
     </row>
-    <row r="378" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B378" t="s">
         <v>27</v>
       </c>
@@ -26364,7 +26370,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="379" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B379" t="s">
         <v>27</v>
       </c>
@@ -26418,7 +26424,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="380" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B380" t="s">
         <v>27</v>
       </c>
@@ -26472,7 +26478,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="381" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B381" t="s">
         <v>27</v>
       </c>
@@ -26526,7 +26532,7 @@
         <v>4.1123760000000003</v>
       </c>
     </row>
-    <row r="382" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B382" t="s">
         <v>27</v>
       </c>
@@ -26580,7 +26586,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="383" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B383" t="s">
         <v>27</v>
       </c>
@@ -26634,7 +26640,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="384" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B384" t="s">
         <v>27</v>
       </c>
@@ -26688,7 +26694,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="385" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B385" t="s">
         <v>27</v>
       </c>
@@ -26742,7 +26748,7 @@
         <v>4.7977719999999993</v>
       </c>
     </row>
-    <row r="386" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B386" t="s">
         <v>27</v>
       </c>
@@ -26796,7 +26802,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="387" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B387" t="s">
         <v>27</v>
       </c>
@@ -26850,7 +26856,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="388" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B388" t="s">
         <v>27</v>
       </c>
@@ -26904,7 +26910,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="389" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B389" t="s">
         <v>27</v>
       </c>
@@ -26958,7 +26964,7 @@
         <v>4.1123760000000003</v>
       </c>
     </row>
-    <row r="390" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B390" t="s">
         <v>27</v>
       </c>
@@ -27012,7 +27018,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="391" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B391" t="s">
         <v>27</v>
       </c>
@@ -27066,7 +27072,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="392" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B392" t="s">
         <v>27</v>
       </c>
@@ -27120,7 +27126,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="393" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B393" t="s">
         <v>27</v>
       </c>
@@ -27174,7 +27180,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="394" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B394" t="s">
         <v>27</v>
       </c>
@@ -27228,7 +27234,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="395" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B395" t="s">
         <v>27</v>
       </c>
@@ -27282,7 +27288,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="396" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B396" t="s">
         <v>62</v>
       </c>
@@ -27336,7 +27342,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="397" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B397" t="s">
         <v>62</v>
       </c>
@@ -27390,7 +27396,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="398" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B398" t="s">
         <v>62</v>
       </c>
@@ -27444,7 +27450,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="399" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B399" t="s">
         <v>62</v>
       </c>
@@ -27498,7 +27504,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="400" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B400" t="s">
         <v>62</v>
       </c>
@@ -27552,7 +27558,7 @@
         <v>4.7977719999999993</v>
       </c>
     </row>
-    <row r="401" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B401" t="s">
         <v>62</v>
       </c>
@@ -27606,7 +27612,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="402" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B402" t="s">
         <v>62</v>
       </c>
@@ -27660,7 +27666,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="403" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B403" t="s">
         <v>62</v>
       </c>
@@ -27714,7 +27720,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="404" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B404" t="s">
         <v>62</v>
       </c>
@@ -27768,7 +27774,7 @@
         <v>4.1123760000000003</v>
       </c>
     </row>
-    <row r="405" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B405" t="s">
         <v>62</v>
       </c>
@@ -27822,7 +27828,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="406" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B406" t="s">
         <v>62</v>
       </c>
@@ -27876,7 +27882,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="407" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B407" t="s">
         <v>62</v>
       </c>
@@ -27930,7 +27936,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="408" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B408" t="s">
         <v>62</v>
       </c>
@@ -27984,7 +27990,7 @@
         <v>4.7977719999999993</v>
       </c>
     </row>
-    <row r="409" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B409" t="s">
         <v>62</v>
       </c>
@@ -28038,7 +28044,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="410" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B410" t="s">
         <v>62</v>
       </c>
@@ -28092,7 +28098,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="411" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B411" t="s">
         <v>62</v>
       </c>
@@ -28146,7 +28152,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="412" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B412" t="s">
         <v>62</v>
       </c>
@@ -28200,7 +28206,7 @@
         <v>4.1123760000000003</v>
       </c>
     </row>
-    <row r="413" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B413" t="s">
         <v>62</v>
       </c>
@@ -28254,7 +28260,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="414" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B414" t="s">
         <v>62</v>
       </c>
@@ -28308,7 +28314,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="415" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B415" t="s">
         <v>62</v>
       </c>
@@ -28362,7 +28368,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="416" spans="2:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B416" t="s">
         <v>62</v>
       </c>
@@ -28416,7 +28422,7 @@
         <v>4.7977719999999993</v>
       </c>
     </row>
-    <row r="417" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B417" t="s">
         <v>62</v>
       </c>
@@ -28470,7 +28476,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="418" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B418" t="s">
         <v>62</v>
       </c>
@@ -28524,7 +28530,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="419" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B419" t="s">
         <v>62</v>
       </c>
@@ -28578,7 +28584,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="420" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A420" s="6">
         <v>2073</v>
       </c>
@@ -28638,7 +28644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A421" s="6">
         <v>2148</v>
       </c>
@@ -28695,7 +28701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A422" s="6">
         <v>2127</v>
       </c>
@@ -28755,7 +28761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A423" s="6">
         <v>2185</v>
       </c>
@@ -28815,7 +28821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A424" s="6">
         <v>1957</v>
       </c>
@@ -28875,7 +28881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A425" s="6">
         <v>2129</v>
       </c>
@@ -28935,7 +28941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A426" s="6">
         <v>2128</v>
       </c>
@@ -28995,7 +29001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A427" s="6">
         <v>2063</v>
       </c>
@@ -29055,7 +29061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A428" s="6">
         <v>2145</v>
       </c>
@@ -29112,7 +29118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A429" s="6">
         <v>2147</v>
       </c>
@@ -29169,7 +29175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A430" s="6">
         <v>2115</v>
       </c>

--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BE902A-1E3C-4BDF-B888-EE95F23C7A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5211F3ED-D36C-4309-82DD-13CD0396C6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3373" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3383" uniqueCount="702">
   <si>
     <t>Grupo</t>
   </si>
@@ -2131,6 +2131,36 @@
   </si>
   <si>
     <t>GAZE CIRCULAR - 13 FIOS</t>
+  </si>
+  <si>
+    <t>75/30</t>
+  </si>
+  <si>
+    <t>60/22</t>
+  </si>
+  <si>
+    <t>40/16</t>
+  </si>
+  <si>
+    <t>90/40</t>
+  </si>
+  <si>
+    <t>100/44</t>
+  </si>
+  <si>
+    <t>50/20</t>
+  </si>
+  <si>
+    <t>70/26</t>
+  </si>
+  <si>
+    <t>90/36</t>
+  </si>
+  <si>
+    <t>110/44</t>
+  </si>
+  <si>
+    <t>110/50</t>
   </si>
 </sst>
 </file>
@@ -8059,9 +8089,8 @@
       <c r="E76" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F76">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>110</v>
+      <c r="F76" t="s">
+        <v>701</v>
       </c>
       <c r="G76" t="s">
         <v>111</v>
@@ -8119,9 +8148,8 @@
       <c r="E77" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F77">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>90</v>
+      <c r="F77" t="s">
+        <v>699</v>
       </c>
       <c r="G77" t="s">
         <v>137</v>
@@ -8179,9 +8207,8 @@
       <c r="E78" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F78">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>70</v>
+      <c r="F78" t="s">
+        <v>698</v>
       </c>
       <c r="G78" t="s">
         <v>149</v>
@@ -8239,9 +8266,8 @@
       <c r="E79" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F79">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>50</v>
+      <c r="F79" t="s">
+        <v>697</v>
       </c>
       <c r="G79" t="s">
         <v>157</v>
@@ -8539,9 +8565,8 @@
       <c r="E84" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F84">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>100</v>
+      <c r="F84" t="s">
+        <v>696</v>
       </c>
       <c r="G84" t="s">
         <v>117</v>
@@ -8599,9 +8624,8 @@
       <c r="E85" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F85">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>75</v>
+      <c r="F85" t="s">
+        <v>692</v>
       </c>
       <c r="G85" t="s">
         <v>145</v>
@@ -8659,9 +8683,8 @@
       <c r="E86" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F86">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>60</v>
+      <c r="F86" t="s">
+        <v>693</v>
       </c>
       <c r="G86" t="s">
         <v>155</v>
@@ -8719,9 +8742,8 @@
       <c r="E87" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F87">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>40</v>
+      <c r="F87" t="s">
+        <v>694</v>
       </c>
       <c r="G87" t="s">
         <v>165</v>
@@ -16022,9 +16044,8 @@
       <c r="E204" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F204">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>90</v>
+      <c r="F204" t="s">
+        <v>695</v>
       </c>
       <c r="G204" t="s">
         <v>132</v>
@@ -16142,9 +16163,8 @@
       <c r="E206" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F206">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>110</v>
+      <c r="F206" t="s">
+        <v>700</v>
       </c>
       <c r="G206" t="s">
         <v>126</v>

--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5211F3ED-D36C-4309-82DD-13CD0396C6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7754D8-0B2E-4413-B981-DBC46947412F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$430</definedName>
+    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$432</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3383" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="704">
   <si>
     <t>Grupo</t>
   </si>
@@ -2161,6 +2161,12 @@
   </si>
   <si>
     <t>110/50</t>
+  </si>
+  <si>
+    <t>GAZE ESTERIL 11 FIOS - 50x91</t>
+  </si>
+  <si>
+    <t>ESTERIL 11 FIOS</t>
   </si>
 </sst>
 </file>
@@ -2401,7 +2407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -2495,6 +2501,7 @@
     <xf numFmtId="44" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -2953,8 +2960,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:Q430" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:Q430" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:Q432" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:Q432" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
   <tableColumns count="17">
     <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2" dataDxfId="34"/>
     <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="33"/>
@@ -3362,7 +3369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868BC1FE-16FA-4E4B-B34E-F84713378B87}">
-  <dimension ref="A1:Q430"/>
+  <dimension ref="A1:Q432"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -28683,42 +28690,44 @@
       <c r="G421" t="s">
         <v>672</v>
       </c>
-      <c r="H421" s="2"/>
+      <c r="H421" s="2">
+        <v>71</v>
+      </c>
       <c r="I421" s="34">
         <f>Tabela14[[#This Row],[PRECO 3%]]+(Tabela14[[#This Row],[PRECO 3%]]*0.06)</f>
-        <v>0</v>
+        <v>75.260000000000005</v>
       </c>
       <c r="J421" s="34">
         <f>(Tabela14[[#This Row],[PRECO 3%]]*0.1)+Tabela14[[#This Row],[PRECO 3%]]</f>
-        <v>0</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="K421" s="34">
         <f>(Tabela14[[#This Row],[REGIÃO01-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO01-3%]]</f>
-        <v>0</v>
+        <v>82.785999999999987</v>
       </c>
       <c r="L421" s="34">
         <f>(Tabela14[[#This Row],[PRECO 3%]]*0.05)+Tabela14[[#This Row],[PRECO 3%]]</f>
-        <v>0</v>
+        <v>74.55</v>
       </c>
       <c r="M421" s="34">
         <f>(Tabela14[[#This Row],[REGIÃO02 - 3%]]*0.06)+Tabela14[[#This Row],[REGIÃO02 - 3%]]</f>
-        <v>0</v>
+        <v>79.022999999999996</v>
       </c>
       <c r="N421" s="34">
         <f>(Tabela14[[#This Row],[PRECO 3%]]*0.08)+Tabela14[[#This Row],[PRECO 3%]]</f>
-        <v>0</v>
+        <v>76.680000000000007</v>
       </c>
       <c r="O421" s="34">
         <f>(Tabela14[[#This Row],[REGIÃO03-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO03-3%]]</f>
-        <v>0</v>
+        <v>81.280800000000013</v>
       </c>
       <c r="P421" s="34">
         <f>(Tabela14[[#This Row],[PRECO 3%]]*0.06)+Tabela14[[#This Row],[PRECO 3%]]</f>
-        <v>0</v>
+        <v>75.260000000000005</v>
       </c>
       <c r="Q421" s="34">
         <f>(Tabela14[[#This Row],[REGIÃO04-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO04-3%]]</f>
-        <v>0</v>
+        <v>79.775600000000011</v>
       </c>
     </row>
     <row r="422" spans="1:17" x14ac:dyDescent="0.25">
@@ -29248,6 +29257,119 @@
         <v>0</v>
       </c>
       <c r="Q430" s="34">
+        <f>(Tabela14[[#This Row],[REGIÃO04-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO04-3%]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A431" s="6">
+        <v>2270</v>
+      </c>
+      <c r="B431" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C431" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D431" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="E431" s="53">
+        <v>650</v>
+      </c>
+      <c r="F431">
+        <v>15</v>
+      </c>
+      <c r="G431" t="s">
+        <v>691</v>
+      </c>
+      <c r="H431" s="2">
+        <v>52.22</v>
+      </c>
+      <c r="I431" s="34">
+        <f>Tabela14[[#This Row],[PRECO 3%]]+(Tabela14[[#This Row],[PRECO 3%]]*0.06)</f>
+        <v>55.353200000000001</v>
+      </c>
+      <c r="J431" s="34">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.1)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>57.442</v>
+      </c>
+      <c r="K431" s="34">
+        <f>(Tabela14[[#This Row],[REGIÃO01-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO01-3%]]</f>
+        <v>60.88852</v>
+      </c>
+      <c r="L431" s="34">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.05)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>54.830999999999996</v>
+      </c>
+      <c r="M431" s="34">
+        <f>(Tabela14[[#This Row],[REGIÃO02 - 3%]]*0.06)+Tabela14[[#This Row],[REGIÃO02 - 3%]]</f>
+        <v>58.120859999999993</v>
+      </c>
+      <c r="N431" s="34">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.08)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>56.397599999999997</v>
+      </c>
+      <c r="O431" s="34">
+        <f>(Tabela14[[#This Row],[REGIÃO03-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO03-3%]]</f>
+        <v>59.781455999999999</v>
+      </c>
+      <c r="P431" s="34">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.06)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>55.353200000000001</v>
+      </c>
+      <c r="Q431" s="34">
+        <f>(Tabela14[[#This Row],[REGIÃO04-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO04-3%]]</f>
+        <v>58.674391999999997</v>
+      </c>
+    </row>
+    <row r="432" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A432" s="6">
+        <v>2183</v>
+      </c>
+      <c r="B432" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="C432" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="D432" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="H432" s="2"/>
+      <c r="I432" s="34">
+        <f>Tabela14[[#This Row],[PRECO 3%]]+(Tabela14[[#This Row],[PRECO 3%]]*0.06)</f>
+        <v>0</v>
+      </c>
+      <c r="J432" s="34">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.1)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>0</v>
+      </c>
+      <c r="K432" s="34">
+        <f>(Tabela14[[#This Row],[REGIÃO01-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO01-3%]]</f>
+        <v>0</v>
+      </c>
+      <c r="L432" s="34">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.05)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>0</v>
+      </c>
+      <c r="M432" s="34">
+        <f>(Tabela14[[#This Row],[REGIÃO02 - 3%]]*0.06)+Tabela14[[#This Row],[REGIÃO02 - 3%]]</f>
+        <v>0</v>
+      </c>
+      <c r="N432" s="34">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.08)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>0</v>
+      </c>
+      <c r="O432" s="34">
+        <f>(Tabela14[[#This Row],[REGIÃO03-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO03-3%]]</f>
+        <v>0</v>
+      </c>
+      <c r="P432" s="34">
+        <f>(Tabela14[[#This Row],[PRECO 3%]]*0.06)+Tabela14[[#This Row],[PRECO 3%]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q432" s="34">
         <f>(Tabela14[[#This Row],[REGIÃO04-3%]]*0.06)+Tabela14[[#This Row],[REGIÃO04-3%]]</f>
         <v>0</v>
       </c>
